--- a/data/trans_camb/P16A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 8,2</t>
+          <t>0,39; 8,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,19</t>
+          <t>-0,17; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 11,0</t>
+          <t>-1,08; 12,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,71</t>
+          <t>-0,13; 9,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 5,03</t>
+          <t>-4,96; 4,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 9,67</t>
+          <t>-3,44; 10,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,87</t>
+          <t>1,4; 7,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,09</t>
+          <t>-1,09; 5,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 7,72</t>
+          <t>-1,25; 7,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 127,83</t>
+          <t>4,06; 144,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 140,08</t>
+          <t>-2,14; 129,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 168,16</t>
+          <t>-14,61; 178,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 74,45</t>
+          <t>-1,35; 64,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 35,8</t>
+          <t>-25,45; 34,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 63,72</t>
+          <t>-18,52; 62,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 71,93</t>
+          <t>10,3; 75,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 47,66</t>
+          <t>-8,56; 51,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 65,82</t>
+          <t>-10,09; 69,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,06</t>
+          <t>2,45; 9,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,44</t>
+          <t>4,22; 11,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,26</t>
+          <t>5,16; 16,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 13,97</t>
+          <t>5,16; 14,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,38</t>
+          <t>3,97; 12,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 9,7</t>
+          <t>-3,54; 9,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,91</t>
+          <t>4,76; 10,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,34</t>
+          <t>5,66; 11,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,21</t>
+          <t>2,68; 11,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 117,83</t>
+          <t>22,29; 127,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,24; 157,53</t>
+          <t>40,74; 160,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,48; 211,75</t>
+          <t>54,99; 212,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,57; 111,11</t>
+          <t>30,68; 111,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 105,11</t>
+          <t>23,78; 97,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 70,29</t>
+          <t>-20,07; 73,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,74; 105,53</t>
+          <t>36,55; 98,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,89; 110,2</t>
+          <t>43,48; 114,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 107,35</t>
+          <t>23,36; 105,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,2</t>
+          <t>-2,74; 5,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 7,83</t>
+          <t>0,19; 7,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,52</t>
+          <t>0,93; 9,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 14,51</t>
+          <t>5,15; 14,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,14</t>
+          <t>-1,34; 7,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,87</t>
+          <t>5,04; 14,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,78</t>
+          <t>2,51; 8,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,42</t>
+          <t>0,46; 6,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 11,2</t>
+          <t>4,23; 10,87</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 42,58</t>
+          <t>-18,78; 42,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 66,57</t>
+          <t>0,56; 65,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,04; 79,31</t>
+          <t>5,96; 83,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,45; 78,32</t>
+          <t>22,15; 81,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 43,88</t>
+          <t>-6,2; 39,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,13; 80,43</t>
+          <t>21,35; 77,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,76; 55,39</t>
+          <t>12,9; 54,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 40,85</t>
+          <t>2,23; 40,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,99; 71,19</t>
+          <t>23,27; 68,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 5,85</t>
+          <t>-3,24; 5,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 8,99</t>
+          <t>0,1; 9,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 11,62</t>
+          <t>-7,89; 12,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 13,41</t>
+          <t>2,44; 13,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 11,22</t>
+          <t>0,13; 10,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 17,76</t>
+          <t>6,08; 18,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,17</t>
+          <t>1,34; 8,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,43</t>
+          <t>1,62; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 13,5</t>
+          <t>-3,56; 13,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 47,57</t>
+          <t>-18,78; 45,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 70,39</t>
+          <t>0,66; 77,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 81,6</t>
+          <t>-45,7; 86,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 64,0</t>
+          <t>8,91; 64,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 54,13</t>
+          <t>0,52; 50,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,14; 84,97</t>
+          <t>23,79; 85,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,1; 45,94</t>
+          <t>6,19; 46,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,29; 47,91</t>
+          <t>7,11; 47,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 73,02</t>
+          <t>-15,56; 71,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 5,22</t>
+          <t>-5,58; 6,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,18</t>
+          <t>-5,17; 5,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 13,34</t>
+          <t>2,06; 13,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 12,91</t>
+          <t>1,11; 13,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 16,79</t>
+          <t>4,42; 16,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,18; 21,4</t>
+          <t>9,87; 21,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,86</t>
+          <t>-0,66; 8,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,99</t>
+          <t>1,46; 10,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,69; 15,72</t>
+          <t>7,86; 15,81</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 26,98</t>
+          <t>-22,39; 32,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 36,8</t>
+          <t>-20,52; 29,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,97; 70,05</t>
+          <t>7,33; 72,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 51,77</t>
+          <t>3,54; 52,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,24; 66,93</t>
+          <t>13,44; 65,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,78; 85,35</t>
+          <t>30,37; 86,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 33,48</t>
+          <t>-2,2; 37,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,42; 42,75</t>
+          <t>4,59; 44,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>27,3; 68,19</t>
+          <t>28,12; 69,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,19; 17,71</t>
+          <t>3,09; 17,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,68</t>
+          <t>-4,7; 6,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,71; 15,96</t>
+          <t>4,99; 16,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,39; 20,62</t>
+          <t>6,41; 20,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,39; 17,3</t>
+          <t>4,41; 17,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,71; 57,27</t>
+          <t>18,43; 57,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,75; 16,74</t>
+          <t>6,48; 16,47</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,29</t>
+          <t>1,38; 10,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14,38; 50,18</t>
+          <t>14,16; 49,91</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15,28; 128,09</t>
+          <t>14,0; 124,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 55,81</t>
+          <t>-24,28; 51,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23,16; 117,24</t>
+          <t>24,92; 122,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,04; 69,03</t>
+          <t>17,82; 70,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,98; 60,9</t>
+          <t>12,35; 61,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55,88; 219,33</t>
+          <t>54,91; 216,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,05; 72,88</t>
+          <t>23,17; 71,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,94; 47,84</t>
+          <t>4,7; 46,19</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54,45; 225,97</t>
+          <t>53,7; 219,11</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 13,64</t>
+          <t>-3,48; 13,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 13,44</t>
+          <t>-1,74; 13,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,87; 20,79</t>
+          <t>5,9; 21,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,55; 19,2</t>
+          <t>4,46; 20,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 15,23</t>
+          <t>-0,67; 16,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,86; 32,24</t>
+          <t>19,01; 31,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,44</t>
+          <t>2,8; 14,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,9; 12,43</t>
+          <t>0,32; 12,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,99; 25,5</t>
+          <t>15,41; 25,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 61,16</t>
+          <t>-11,47; 61,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 59,99</t>
+          <t>-5,85; 63,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,07; 94,71</t>
+          <t>18,02; 98,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,39; 50,8</t>
+          <t>9,94; 56,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 39,49</t>
+          <t>-1,44; 43,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,34; 87,26</t>
+          <t>40,84; 86,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,6; 43,6</t>
+          <t>7,13; 43,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,32; 39,14</t>
+          <t>1,36; 38,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>37,71; 79,75</t>
+          <t>38,87; 78,81</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,74</t>
+          <t>2,18; 5,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,7</t>
+          <t>3,12; 6,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,11</t>
+          <t>2,87; 11,23</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,72</t>
+          <t>7,61; 11,95</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,19</t>
+          <t>5,14; 9,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,82; 29,23</t>
+          <t>13,41; 27,81</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,21</t>
+          <t>5,43; 8,31</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,63</t>
+          <t>4,7; 7,62</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,12</t>
+          <t>10,04; 19,45</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,09; 43,93</t>
+          <t>14,62; 45,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>21,14; 50,37</t>
+          <t>20,98; 51,52</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27,65; 84,54</t>
+          <t>22,65; 84,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30,33; 50,89</t>
+          <t>30,47; 53,22</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,12; 40,06</t>
+          <t>20,29; 41,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>56,71; 123,79</t>
+          <t>55,0; 116,79</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,83; 45,22</t>
+          <t>27,83; 45,4</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>24,07; 41,73</t>
+          <t>23,57; 41,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>52,09; 105,95</t>
+          <t>50,89; 102,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>3,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 8,43</t>
+          <t>0,1; 8,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,25</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 12,24</t>
+          <t>-1,13; 9,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,78</t>
+          <t>-0,22; 10,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 4,99</t>
+          <t>-4,7; 4,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 10,18</t>
+          <t>-3,35; 10,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,98</t>
+          <t>1,66; 8,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,62</t>
+          <t>-0,98; 5,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,86</t>
+          <t>-0,76; 8,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 144,58</t>
+          <t>-0,34; 136,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 129,56</t>
+          <t>-1,39; 126,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 178,38</t>
+          <t>-16,68; 153,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 64,01</t>
+          <t>-1,44; 67,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 34,51</t>
+          <t>-24,91; 33,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 62,5</t>
+          <t>-17,16; 67,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 75,52</t>
+          <t>11,84; 72,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 51,2</t>
+          <t>-8,06; 46,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 69,17</t>
+          <t>-6,25; 71,82</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>8,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,35</t>
+          <t>2,61; 9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 11,93</t>
+          <t>4,23; 11,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 16,07</t>
+          <t>4,96; 15,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,39</t>
+          <t>4,69; 14,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 12,84</t>
+          <t>3,74; 13,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 9,91</t>
+          <t>0,85; 10,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,31</t>
+          <t>4,84; 10,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,81</t>
+          <t>5,51; 11,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 11,36</t>
+          <t>4,56; 11,64</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117,58%</t>
+          <t>112,62%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,29; 127,32</t>
+          <t>24,69; 127,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,74; 160,15</t>
+          <t>41,29; 158,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,99; 212,1</t>
+          <t>48,98; 207,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,68; 111,95</t>
+          <t>29,9; 111,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,78; 97,76</t>
+          <t>22,23; 104,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 73,01</t>
+          <t>4,96; 79,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,55; 98,37</t>
+          <t>37,3; 106,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,48; 114,15</t>
+          <t>42,56; 110,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,36; 105,55</t>
+          <t>34,53; 109,24</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,2</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,22</t>
+          <t>-2,52; 4,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,63</t>
+          <t>-0,19; 7,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,92</t>
+          <t>0,52; 8,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 14,9</t>
+          <t>5,24; 15,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,55</t>
+          <t>-1,02; 8,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 14,54</t>
+          <t>5,1; 13,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,64</t>
+          <t>2,79; 8,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,35</t>
+          <t>0,44; 6,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,87</t>
+          <t>3,97; 10,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 42,3</t>
+          <t>-15,99; 41,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 65,93</t>
+          <t>-1,25; 66,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 83,38</t>
+          <t>3,39; 74,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 81,85</t>
+          <t>22,25; 83,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 39,78</t>
+          <t>-4,33; 44,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,35; 77,27</t>
+          <t>21,62; 76,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,9; 54,33</t>
+          <t>14,72; 56,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 40,44</t>
+          <t>1,65; 39,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,27; 68,46</t>
+          <t>20,48; 63,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,85</t>
+          <t>13,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,21</t>
+          <t>12,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,71</t>
+          <t>-2,78; 6,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 9,31</t>
+          <t>0,03; 8,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 12,13</t>
+          <t>5,25; 14,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 13,59</t>
+          <t>2,55; 13,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 10,57</t>
+          <t>-0,16; 10,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 18,28</t>
+          <t>8,93; 18,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,25</t>
+          <t>1,01; 8,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,38</t>
+          <t>1,47; 8,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 13,3</t>
+          <t>8,69; 15,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 45,83</t>
+          <t>-15,91; 50,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 77,16</t>
+          <t>-0,35; 69,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 86,95</t>
+          <t>29,79; 116,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 64,92</t>
+          <t>9,59; 65,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 50,1</t>
+          <t>-0,54; 51,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,79; 85,38</t>
+          <t>32,13; 88,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 46,37</t>
+          <t>5,1; 48,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 47,91</t>
+          <t>6,75; 50,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 71,53</t>
+          <t>41,08; 90,46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,47</t>
+          <t>15,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 6,29</t>
+          <t>-6,14; 5,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,7</t>
+          <t>-5,67; 5,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 13,69</t>
+          <t>2,46; 13,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 13,3</t>
+          <t>0,27; 13,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 16,92</t>
+          <t>4,03; 16,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,87; 21,01</t>
+          <t>9,36; 21,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 8,51</t>
+          <t>-1,09; 7,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,23</t>
+          <t>1,06; 9,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,81</t>
+          <t>7,56; 15,1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 32,59</t>
+          <t>-24,45; 29,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 29,84</t>
+          <t>-22,53; 30,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,33; 72,66</t>
+          <t>9,85; 70,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,54; 52,91</t>
+          <t>1,07; 53,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,44; 65,58</t>
+          <t>12,98; 66,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,37; 86,23</t>
+          <t>28,41; 85,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 37,05</t>
+          <t>-4,18; 32,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,59; 44,58</t>
+          <t>3,92; 43,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,12; 69,45</t>
+          <t>27,12; 64,29</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10,91</t>
+          <t>10,39</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,31</t>
+          <t>20,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28,04</t>
+          <t>15,21</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,35</t>
+          <t>2,97; 16,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 6,94</t>
+          <t>-4,63; 7,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,99; 16,61</t>
+          <t>4,88; 16,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,41; 20,28</t>
+          <t>5,8; 19,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,41; 17,45</t>
+          <t>3,98; 17,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,43; 57,91</t>
+          <t>14,67; 26,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,47</t>
+          <t>6,6; 16,47</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,66</t>
+          <t>0,93; 10,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14,16; 49,91</t>
+          <t>10,76; 19,45</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>112,21%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>111,72%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14,0; 124,99</t>
+          <t>14,72; 119,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 51,24</t>
+          <t>-24,16; 51,96</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24,92; 122,87</t>
+          <t>23,54; 119,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17,82; 70,53</t>
+          <t>16,65; 67,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,35; 61,13</t>
+          <t>11,27; 62,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,91; 216,15</t>
+          <t>39,55; 94,77</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,17; 71,79</t>
+          <t>23,64; 72,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,7; 46,19</t>
+          <t>3,48; 46,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53,7; 219,11</t>
+          <t>39,13; 87,54</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13,78</t>
+          <t>13,35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,36</t>
+          <t>24,89</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20,53</t>
+          <t>20,04</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 13,81</t>
+          <t>-3,47; 13,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 13,49</t>
+          <t>-1,28; 14,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,9; 21,06</t>
+          <t>5,83; 20,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,46; 20,23</t>
+          <t>3,37; 18,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 16,01</t>
+          <t>-0,53; 15,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,01; 31,49</t>
+          <t>17,89; 30,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,8; 14,26</t>
+          <t>3,04; 14,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 12,59</t>
+          <t>1,18; 12,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,41; 25,65</t>
+          <t>14,67; 25,24</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 61,24</t>
+          <t>-11,54; 60,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 63,2</t>
+          <t>-4,16; 63,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,02; 98,61</t>
+          <t>17,64; 90,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,94; 56,01</t>
+          <t>7,07; 49,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 43,67</t>
+          <t>-1,29; 40,97</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40,84; 86,21</t>
+          <t>37,77; 83,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,13; 43,43</t>
+          <t>7,65; 45,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,36; 38,31</t>
+          <t>3,21; 38,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38,87; 78,81</t>
+          <t>35,95; 77,61</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,07</t>
+          <t>15,09</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,96</t>
+          <t>2,13; 5,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,8</t>
+          <t>3,32; 6,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,23</t>
+          <t>7,87; 12,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,95</t>
+          <t>7,47; 12,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,51</t>
+          <t>5,04; 9,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,41; 27,81</t>
+          <t>13,09; 17,07</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,31</t>
+          <t>5,36; 8,26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,62</t>
+          <t>4,73; 7,64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,45</t>
+          <t>11,32; 14,12</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,62; 45,72</t>
+          <t>14,67; 44,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>20,98; 51,52</t>
+          <t>22,1; 50,77</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22,65; 84,33</t>
+          <t>54,15; 92,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30,47; 53,22</t>
+          <t>29,9; 53,08</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,29; 41,24</t>
+          <t>20,26; 41,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,0; 116,79</t>
+          <t>52,58; 75,6</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,83; 45,4</t>
+          <t>27,44; 45,23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>23,57; 41,77</t>
+          <t>23,71; 41,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>50,89; 102,13</t>
+          <t>57,45; 77,62</t>
         </is>
       </c>
     </row>
